--- a/給与管理システム_v3.xlsx
+++ b/給与管理システム_v3.xlsx
@@ -282,11 +282,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="FF006100"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00FF0000"/>
+      <color rgb="FFFF0000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -294,55 +294,55 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F0000"/>
+      <color rgb="FF7F0000"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F0000"/>
+      <color rgb="FF7F0000"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00000000"/>
+      <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="007F0000"/>
+      <color rgb="FF7F0000"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="FF1F4E79"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="13"/>
     </font>
   </fonts>
@@ -421,42 +421,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
+        <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
+        <fgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1052,14 +1052,14 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2F5496"/>
       <rgbColor rgb="FF375623"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>

--- a/給与管理システム_v3.xlsx
+++ b/給与管理システム_v3.xlsx
@@ -2341,9 +2341,10 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="C7" s="87">
-        <f>VLOOKUP(社員ID,マスタ,2)</f>
-        <v/>
+      <c r="C7" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(社員ID,マスタ,2)</t>
+        </is>
       </c>
       <c r="D7" s="87" t="inlineStr">
         <is>
@@ -2367,9 +2368,10 @@
           <t>雇用区分</t>
         </is>
       </c>
-      <c r="C8" s="87">
-        <f>VLOOKUP(社員ID,マスタ,4)</f>
-        <v/>
+      <c r="C8" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(社員ID,マスタ,4)</t>
+        </is>
       </c>
       <c r="D8" s="87" t="inlineStr">
         <is>
@@ -2393,9 +2395,10 @@
           <t>基本給/日給単価</t>
         </is>
       </c>
-      <c r="C9" s="87">
-        <f>VLOOKUP(マスタF列)</f>
-        <v/>
+      <c r="C9" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(マスタF列)</t>
+        </is>
       </c>
       <c r="D9" s="87" t="inlineStr">
         <is>
@@ -2419,9 +2422,10 @@
           <t>出勤日数</t>
         </is>
       </c>
-      <c r="C10" s="87">
-        <f>VLOOKUP(→月次集計C)</f>
-        <v/>
+      <c r="C10" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(→月次集計C)</t>
+        </is>
       </c>
       <c r="D10" s="87" t="inlineStr">
         <is>
@@ -2445,9 +2449,10 @@
           <t>残業時間</t>
         </is>
       </c>
-      <c r="C11" s="87">
-        <f>VLOOKUP(→月次集計H)</f>
-        <v/>
+      <c r="C11" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(→月次集計H)</t>
+        </is>
       </c>
       <c r="D11" s="87" t="inlineStr">
         <is>
@@ -2471,9 +2476,10 @@
           <t>有給日数</t>
         </is>
       </c>
-      <c r="C12" s="87">
-        <f>VLOOKUP(→月次集計E)</f>
-        <v/>
+      <c r="C12" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(→月次集計E)</t>
+        </is>
       </c>
       <c r="D12" s="87" t="inlineStr">
         <is>
@@ -2526,9 +2532,10 @@
           <t>残業手当</t>
         </is>
       </c>
-      <c r="C14" s="87">
-        <f>マスタG(時給)×F(残業時間)×1.25</f>
-        <v/>
+      <c r="C14" s="87" t="inlineStr">
+        <is>
+          <t>マスタG(時給)×F(残業時間)×1.25</t>
+        </is>
       </c>
       <c r="D14" s="87" t="inlineStr">
         <is>
@@ -2580,9 +2587,10 @@
           <t>総支給額</t>
         </is>
       </c>
-      <c r="C16" s="87">
-        <f>H+I+J</f>
-        <v/>
+      <c r="C16" s="87" t="inlineStr">
+        <is>
+          <t>H+I+J</t>
+        </is>
       </c>
       <c r="D16" s="87" t="inlineStr">
         <is>
@@ -2606,9 +2614,10 @@
           <t>健康保険料</t>
         </is>
       </c>
-      <c r="C17" s="87">
-        <f>VLOOKUP(マスタH列)</f>
-        <v/>
+      <c r="C17" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(マスタH列)</t>
+        </is>
       </c>
       <c r="D17" s="87" t="inlineStr">
         <is>
@@ -2632,9 +2641,10 @@
           <t>厚生年金</t>
         </is>
       </c>
-      <c r="C18" s="87">
-        <f>VLOOKUP(マスタI列)</f>
-        <v/>
+      <c r="C18" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(マスタI列)</t>
+        </is>
       </c>
       <c r="D18" s="87" t="inlineStr">
         <is>
@@ -2658,9 +2668,10 @@
           <t>雇用保険料</t>
         </is>
       </c>
-      <c r="C19" s="87">
-        <f>ROUND(K×マスタJ（雇用保険率）,0)</f>
-        <v/>
+      <c r="C19" s="87" t="inlineStr">
+        <is>
+          <t>ROUND(K×マスタJ（雇用保険率）,0)</t>
+        </is>
       </c>
       <c r="D19" s="87" t="inlineStr">
         <is>
@@ -2684,9 +2695,10 @@
           <t>所得税</t>
         </is>
       </c>
-      <c r="C20" s="87">
-        <f>VLOOKUP(マスタK列)</f>
-        <v/>
+      <c r="C20" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(マスタK列)</t>
+        </is>
       </c>
       <c r="D20" s="87" t="inlineStr">
         <is>
@@ -2711,9 +2723,10 @@
 (住民税前)</t>
         </is>
       </c>
-      <c r="C21" s="87">
-        <f>K-L-M-N-O</f>
-        <v/>
+      <c r="C21" s="87" t="inlineStr">
+        <is>
+          <t>K-L-M-N-O</t>
+        </is>
       </c>
       <c r="D21" s="87" t="inlineStr">
         <is>
@@ -2737,9 +2750,10 @@
           <t>住民税</t>
         </is>
       </c>
-      <c r="C22" s="87">
-        <f>VLOOKUP(マスタL列)</f>
-        <v/>
+      <c r="C22" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(マスタL列)</t>
+        </is>
       </c>
       <c r="D22" s="87" t="inlineStr">
         <is>
@@ -2763,9 +2777,10 @@
           <t>友愛会費</t>
         </is>
       </c>
-      <c r="C23" s="87">
-        <f>VLOOKUP(マスタM列)</f>
-        <v/>
+      <c r="C23" s="87" t="inlineStr">
+        <is>
+          <t>VLOOKUP(マスタM列)</t>
+        </is>
       </c>
       <c r="D23" s="87" t="inlineStr">
         <is>
@@ -2817,9 +2832,10 @@
           <t>手取金額（最終）</t>
         </is>
       </c>
-      <c r="C25" s="87">
-        <f>P-Q-R-S</f>
-        <v/>
+      <c r="C25" s="87" t="inlineStr">
+        <is>
+          <t>P-Q-R-S</t>
+        </is>
       </c>
       <c r="D25" s="87" t="inlineStr">
         <is>

--- a/給与管理システム_v3.xlsx
+++ b/給与管理システム_v3.xlsx
@@ -13800,56 +13800,62 @@
       </c>
       <c r="K3" s="29" t="inlineStr">
         <is>
+          <t>欠勤
+控除</t>
+        </is>
+      </c>
+      <c r="L3" s="29" t="inlineStr">
+        <is>
           <t>総支給</t>
         </is>
       </c>
-      <c r="L3" s="29" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t>健康
 保険</t>
         </is>
       </c>
-      <c r="M3" s="29" t="inlineStr">
+      <c r="N3" s="29" t="inlineStr">
         <is>
           <t>厚生
 年金</t>
         </is>
       </c>
-      <c r="N3" s="29" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t>雇用
 保険</t>
         </is>
       </c>
-      <c r="O3" s="29" t="inlineStr">
+      <c r="P3" s="29" t="inlineStr">
         <is>
           <t>所得税</t>
         </is>
       </c>
-      <c r="P3" s="98" t="inlineStr">
+      <c r="Q3" s="98" t="inlineStr">
         <is>
           <t>控除後支給額
 (住民税前)</t>
         </is>
       </c>
-      <c r="Q3" s="98" t="inlineStr">
+      <c r="R3" s="98" t="inlineStr">
         <is>
           <t>住民税
 (固定月額)</t>
         </is>
       </c>
-      <c r="R3" s="98" t="inlineStr">
+      <c r="S3" s="98" t="inlineStr">
         <is>
           <t>友愛会費</t>
         </is>
       </c>
-      <c r="S3" s="120" t="inlineStr">
+      <c r="T3" s="120" t="inlineStr">
         <is>
           <t>★立替金
 (手動入力)</t>
         </is>
       </c>
-      <c r="T3" s="121" t="inlineStr">
+      <c r="U3" s="121" t="inlineStr">
         <is>
           <t>手取金額
 (最終)</t>
@@ -13887,53 +13893,57 @@
         <v/>
       </c>
       <c r="H4" s="32">
-        <f>IF(C4="月給",D4,IF(C4="日給",D4*E4,IF(C4="時給",IFERROR(VLOOKUP(A4,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A4,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C4="月給",D4,IF(C4="日給",D4*E4+IFERROR(VLOOKUP(A4,従業員マスタ!$A:$G,7,0),0)*G4*8,IF(C4="時給",IFERROR(VLOOKUP(A4,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A4,月次集計!$A:$T,20,0),0)+G4*5),0),0)))</f>
         <v/>
       </c>
       <c r="I4" s="32">
-        <f>IFERROR(VLOOKUP(A4,従業員マスタ!$A:$G,7,0)*F4*1.25,0)</f>
+        <f>IF(OR(A4="EMP001",A4="EMP002"),0,IF(C4="時給",0,IFERROR(VLOOKUP(A4,従業員マスタ!$A:$G,7,0)*F4*1.25,0)))</f>
         <v/>
       </c>
       <c r="J4" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="32">
-        <f>H4+I4+J4</f>
+        <f>IF(OR(A4="EMP008",A4="EMP009",A4="EMP010",A4="EMP011",A4="EMP012",A4="EMP016"),IFERROR(VLOOKUP(A4,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A4,月次集計!$A:$G,7,0)*8+VLOOKUP(A4,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L4" s="32">
+        <f>H4+I4+J4-K4</f>
+        <v/>
+      </c>
+      <c r="M4" s="32">
         <f>IFERROR(VLOOKUP(A4,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M4" s="32">
+      <c r="N4" s="32">
         <f>IFERROR(VLOOKUP(A4,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N4" s="32">
-        <f>IFERROR(ROUND(K4*VLOOKUP(A4,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O4" s="32">
+        <f>IFERROR(ROUND(L4*VLOOKUP(A4,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P4" s="32">
         <f>IFERROR(VLOOKUP(A4,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P4" s="32">
-        <f>K4-L4-M4-N4-O4</f>
-        <v/>
-      </c>
-      <c r="Q4" s="122">
+      <c r="Q4" s="32">
+        <f>L4-M4-N4-O4-P4</f>
+        <v/>
+      </c>
+      <c r="R4" s="122">
         <f>IFERROR(VLOOKUP(A4,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R4" s="122">
+      <c r="S4" s="122">
         <f>IFERROR(VLOOKUP(A4,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S4" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="124">
-        <f>P4-Q4-R4-S4</f>
+      <c r="T4" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="124">
+        <f>Q4-R4-S4-T4</f>
         <v/>
       </c>
     </row>
@@ -13968,53 +13978,57 @@
         <v/>
       </c>
       <c r="H5" s="5">
-        <f>IF(C5="月給",D5,IF(C5="日給",D5*E5,IF(C5="時給",IFERROR(VLOOKUP(A5,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A5,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C5="月給",D5,IF(C5="日給",D5*E5+IFERROR(VLOOKUP(A5,従業員マスタ!$A:$G,7,0),0)*G5*8,IF(C5="時給",IFERROR(VLOOKUP(A5,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A5,月次集計!$A:$T,20,0),0)+G5*5),0),0)))</f>
         <v/>
       </c>
       <c r="I5" s="5">
-        <f>IFERROR(VLOOKUP(A5,従業員マスタ!$A:$G,7,0)*F5*1.25,0)</f>
+        <f>IF(OR(A5="EMP001",A5="EMP002"),0,IF(C5="時給",0,IFERROR(VLOOKUP(A5,従業員マスタ!$A:$G,7,0)*F5*1.25,0)))</f>
         <v/>
       </c>
       <c r="J5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="5">
-        <f>H5+I5+J5</f>
+      <c r="K5" s="32">
+        <f>IF(OR(A5="EMP008",A5="EMP009",A5="EMP010",A5="EMP011",A5="EMP012",A5="EMP016"),IFERROR(VLOOKUP(A5,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A5,月次集計!$A:$G,7,0)*8+VLOOKUP(A5,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L5" s="5">
+        <f>H5+I5+J5-K5</f>
+        <v/>
+      </c>
+      <c r="M5" s="5">
         <f>IFERROR(VLOOKUP(A5,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M5" s="5">
+      <c r="N5" s="5">
         <f>IFERROR(VLOOKUP(A5,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N5" s="5">
-        <f>IFERROR(ROUND(K5*VLOOKUP(A5,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O5" s="5">
+        <f>IFERROR(ROUND(L5*VLOOKUP(A5,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P5" s="5">
         <f>IFERROR(VLOOKUP(A5,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P5" s="5">
-        <f>K5-L5-M5-N5-O5</f>
-        <v/>
-      </c>
-      <c r="Q5" s="122">
+      <c r="Q5" s="5">
+        <f>L5-M5-N5-O5-P5</f>
+        <v/>
+      </c>
+      <c r="R5" s="122">
         <f>IFERROR(VLOOKUP(A5,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R5" s="122">
+      <c r="S5" s="122">
         <f>IFERROR(VLOOKUP(A5,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S5" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="124">
-        <f>P5-Q5-R5-S5</f>
+      <c r="T5" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="124">
+        <f>Q5-R5-S5-T5</f>
         <v/>
       </c>
     </row>
@@ -14049,53 +14063,57 @@
         <v/>
       </c>
       <c r="H6" s="32">
-        <f>IF(C6="月給",D6,IF(C6="日給",D6*E6,IF(C6="時給",IFERROR(VLOOKUP(A6,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A6,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C6="月給",D6,IF(C6="日給",D6*E6+IFERROR(VLOOKUP(A6,従業員マスタ!$A:$G,7,0),0)*G6*8,IF(C6="時給",IFERROR(VLOOKUP(A6,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A6,月次集計!$A:$T,20,0),0)+G6*5),0),0)))</f>
         <v/>
       </c>
       <c r="I6" s="32">
-        <f>IFERROR(VLOOKUP(A6,従業員マスタ!$A:$G,7,0)*F6*1.25,0)</f>
+        <f>IF(OR(A6="EMP001",A6="EMP002"),0,IF(C6="時給",0,IFERROR(VLOOKUP(A6,従業員マスタ!$A:$G,7,0)*F6*1.25,0)))</f>
         <v/>
       </c>
       <c r="J6" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="32">
-        <f>H6+I6+J6</f>
+        <f>IF(OR(A6="EMP008",A6="EMP009",A6="EMP010",A6="EMP011",A6="EMP012",A6="EMP016"),IFERROR(VLOOKUP(A6,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A6,月次集計!$A:$G,7,0)*8+VLOOKUP(A6,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L6" s="32">
+        <f>H6+I6+J6-K6</f>
+        <v/>
+      </c>
+      <c r="M6" s="32">
         <f>IFERROR(VLOOKUP(A6,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M6" s="32">
+      <c r="N6" s="32">
         <f>IFERROR(VLOOKUP(A6,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N6" s="32">
-        <f>IFERROR(ROUND(K6*VLOOKUP(A6,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O6" s="32">
+        <f>IFERROR(ROUND(L6*VLOOKUP(A6,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P6" s="32">
         <f>IFERROR(VLOOKUP(A6,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P6" s="32">
-        <f>K6-L6-M6-N6-O6</f>
-        <v/>
-      </c>
-      <c r="Q6" s="122">
+      <c r="Q6" s="32">
+        <f>L6-M6-N6-O6-P6</f>
+        <v/>
+      </c>
+      <c r="R6" s="122">
         <f>IFERROR(VLOOKUP(A6,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R6" s="122">
+      <c r="S6" s="122">
         <f>IFERROR(VLOOKUP(A6,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S6" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="124">
-        <f>P6-Q6-R6-S6</f>
+      <c r="T6" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="124">
+        <f>Q6-R6-S6-T6</f>
         <v/>
       </c>
     </row>
@@ -14130,53 +14148,57 @@
         <v/>
       </c>
       <c r="H7" s="5">
-        <f>IF(C7="月給",D7,IF(C7="日給",D7*E7,IF(C7="時給",IFERROR(VLOOKUP(A7,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A7,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C7="月給",D7,IF(C7="日給",D7*E7+IFERROR(VLOOKUP(A7,従業員マスタ!$A:$G,7,0),0)*G7*8,IF(C7="時給",IFERROR(VLOOKUP(A7,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A7,月次集計!$A:$T,20,0),0)+G7*5),0),0)))</f>
         <v/>
       </c>
       <c r="I7" s="5">
-        <f>IFERROR(VLOOKUP(A7,従業員マスタ!$A:$G,7,0)*F7*1.25,0)</f>
+        <f>IF(OR(A7="EMP001",A7="EMP002"),0,IF(C7="時給",0,IFERROR(VLOOKUP(A7,従業員マスタ!$A:$G,7,0)*F7*1.25,0)))</f>
         <v/>
       </c>
       <c r="J7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="5">
-        <f>H7+I7+J7</f>
+      <c r="K7" s="32">
+        <f>IF(OR(A7="EMP008",A7="EMP009",A7="EMP010",A7="EMP011",A7="EMP012",A7="EMP016"),IFERROR(VLOOKUP(A7,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A7,月次集計!$A:$G,7,0)*8+VLOOKUP(A7,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L7" s="5">
+        <f>H7+I7+J7-K7</f>
+        <v/>
+      </c>
+      <c r="M7" s="5">
         <f>IFERROR(VLOOKUP(A7,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M7" s="5">
+      <c r="N7" s="5">
         <f>IFERROR(VLOOKUP(A7,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N7" s="5">
-        <f>IFERROR(ROUND(K7*VLOOKUP(A7,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O7" s="5">
+        <f>IFERROR(ROUND(L7*VLOOKUP(A7,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P7" s="5">
         <f>IFERROR(VLOOKUP(A7,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P7" s="5">
-        <f>K7-L7-M7-N7-O7</f>
-        <v/>
-      </c>
-      <c r="Q7" s="122">
+      <c r="Q7" s="5">
+        <f>L7-M7-N7-O7-P7</f>
+        <v/>
+      </c>
+      <c r="R7" s="122">
         <f>IFERROR(VLOOKUP(A7,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R7" s="122">
+      <c r="S7" s="122">
         <f>IFERROR(VLOOKUP(A7,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S7" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="124">
-        <f>P7-Q7-R7-S7</f>
+      <c r="T7" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="124">
+        <f>Q7-R7-S7-T7</f>
         <v/>
       </c>
     </row>
@@ -14211,53 +14233,57 @@
         <v/>
       </c>
       <c r="H8" s="32">
-        <f>IF(C8="月給",D8,IF(C8="日給",D8*E8,IF(C8="時給",IFERROR(VLOOKUP(A8,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A8,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C8="月給",D8,IF(C8="日給",D8*E8+IFERROR(VLOOKUP(A8,従業員マスタ!$A:$G,7,0),0)*G8*8,IF(C8="時給",IFERROR(VLOOKUP(A8,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A8,月次集計!$A:$T,20,0),0)+G8*5),0),0)))</f>
         <v/>
       </c>
       <c r="I8" s="32">
-        <f>IFERROR(VLOOKUP(A8,従業員マスタ!$A:$G,7,0)*F8*1.25,0)</f>
+        <f>IF(OR(A8="EMP001",A8="EMP002"),0,IF(C8="時給",0,IFERROR(VLOOKUP(A8,従業員マスタ!$A:$G,7,0)*F8*1.25,0)))</f>
         <v/>
       </c>
       <c r="J8" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="32">
-        <f>H8+I8+J8</f>
+        <f>IF(OR(A8="EMP008",A8="EMP009",A8="EMP010",A8="EMP011",A8="EMP012",A8="EMP016"),IFERROR(VLOOKUP(A8,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A8,月次集計!$A:$G,7,0)*8+VLOOKUP(A8,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L8" s="32">
+        <f>H8+I8+J8-K8</f>
+        <v/>
+      </c>
+      <c r="M8" s="32">
         <f>IFERROR(VLOOKUP(A8,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M8" s="32">
+      <c r="N8" s="32">
         <f>IFERROR(VLOOKUP(A8,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N8" s="32">
-        <f>IFERROR(ROUND(K8*VLOOKUP(A8,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O8" s="32">
+        <f>IFERROR(ROUND(L8*VLOOKUP(A8,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P8" s="32">
         <f>IFERROR(VLOOKUP(A8,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P8" s="32">
-        <f>K8-L8-M8-N8-O8</f>
-        <v/>
-      </c>
-      <c r="Q8" s="122">
+      <c r="Q8" s="32">
+        <f>L8-M8-N8-O8-P8</f>
+        <v/>
+      </c>
+      <c r="R8" s="122">
         <f>IFERROR(VLOOKUP(A8,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R8" s="122">
+      <c r="S8" s="122">
         <f>IFERROR(VLOOKUP(A8,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S8" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="124">
-        <f>P8-Q8-R8-S8</f>
+      <c r="T8" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="124">
+        <f>Q8-R8-S8-T8</f>
         <v/>
       </c>
     </row>
@@ -14292,53 +14318,57 @@
         <v/>
       </c>
       <c r="H9" s="5">
-        <f>IF(C9="月給",D9,IF(C9="日給",D9*E9,IF(C9="時給",IFERROR(VLOOKUP(A9,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A9,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C9="月給",D9,IF(C9="日給",D9*E9+IFERROR(VLOOKUP(A9,従業員マスタ!$A:$G,7,0),0)*G9*8,IF(C9="時給",IFERROR(VLOOKUP(A9,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A9,月次集計!$A:$T,20,0),0)+G9*5),0),0)))</f>
         <v/>
       </c>
       <c r="I9" s="5">
-        <f>IFERROR(VLOOKUP(A9,従業員マスタ!$A:$G,7,0)*F9*1.25,0)</f>
+        <f>IF(OR(A9="EMP001",A9="EMP002"),0,IF(C9="時給",0,IFERROR(VLOOKUP(A9,従業員マスタ!$A:$G,7,0)*F9*1.25,0)))</f>
         <v/>
       </c>
       <c r="J9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="5">
-        <f>H9+I9+J9</f>
+      <c r="K9" s="32">
+        <f>IF(OR(A9="EMP008",A9="EMP009",A9="EMP010",A9="EMP011",A9="EMP012",A9="EMP016"),IFERROR(VLOOKUP(A9,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A9,月次集計!$A:$G,7,0)*8+VLOOKUP(A9,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L9" s="5">
+        <f>H9+I9+J9-K9</f>
+        <v/>
+      </c>
+      <c r="M9" s="5">
         <f>IFERROR(VLOOKUP(A9,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M9" s="5">
+      <c r="N9" s="5">
         <f>IFERROR(VLOOKUP(A9,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N9" s="5">
-        <f>IFERROR(ROUND(K9*VLOOKUP(A9,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O9" s="5">
+        <f>IFERROR(ROUND(L9*VLOOKUP(A9,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P9" s="5">
         <f>IFERROR(VLOOKUP(A9,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P9" s="5">
-        <f>K9-L9-M9-N9-O9</f>
-        <v/>
-      </c>
-      <c r="Q9" s="122">
+      <c r="Q9" s="5">
+        <f>L9-M9-N9-O9-P9</f>
+        <v/>
+      </c>
+      <c r="R9" s="122">
         <f>IFERROR(VLOOKUP(A9,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R9" s="122">
+      <c r="S9" s="122">
         <f>IFERROR(VLOOKUP(A9,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S9" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="124">
-        <f>P9-Q9-R9-S9</f>
+      <c r="T9" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="124">
+        <f>Q9-R9-S9-T9</f>
         <v/>
       </c>
     </row>
@@ -14373,53 +14403,57 @@
         <v/>
       </c>
       <c r="H10" s="32">
-        <f>IF(C10="月給",D10,IF(C10="日給",D10*E10,IF(C10="時給",IFERROR(VLOOKUP(A10,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A10,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C10="月給",D10,IF(C10="日給",D10*E10+IFERROR(VLOOKUP(A10,従業員マスタ!$A:$G,7,0),0)*G10*8,IF(C10="時給",IFERROR(VLOOKUP(A10,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A10,月次集計!$A:$T,20,0),0)+G10*5),0),0)))</f>
         <v/>
       </c>
       <c r="I10" s="32">
-        <f>IFERROR(VLOOKUP(A10,従業員マスタ!$A:$G,7,0)*F10*1.25,0)</f>
+        <f>IF(OR(A10="EMP001",A10="EMP002"),0,IF(C10="時給",0,IFERROR(VLOOKUP(A10,従業員マスタ!$A:$G,7,0)*F10*1.25,0)))</f>
         <v/>
       </c>
       <c r="J10" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="32">
-        <f>H10+I10+J10</f>
+        <f>IF(OR(A10="EMP008",A10="EMP009",A10="EMP010",A10="EMP011",A10="EMP012",A10="EMP016"),IFERROR(VLOOKUP(A10,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A10,月次集計!$A:$G,7,0)*8+VLOOKUP(A10,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L10" s="32">
+        <f>H10+I10+J10-K10</f>
+        <v/>
+      </c>
+      <c r="M10" s="32">
         <f>IFERROR(VLOOKUP(A10,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M10" s="32">
+      <c r="N10" s="32">
         <f>IFERROR(VLOOKUP(A10,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N10" s="32">
-        <f>IFERROR(ROUND(K10*VLOOKUP(A10,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O10" s="32">
+        <f>IFERROR(ROUND(L10*VLOOKUP(A10,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P10" s="32">
         <f>IFERROR(VLOOKUP(A10,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P10" s="32">
-        <f>K10-L10-M10-N10-O10</f>
-        <v/>
-      </c>
-      <c r="Q10" s="122">
+      <c r="Q10" s="32">
+        <f>L10-M10-N10-O10-P10</f>
+        <v/>
+      </c>
+      <c r="R10" s="122">
         <f>IFERROR(VLOOKUP(A10,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R10" s="122">
+      <c r="S10" s="122">
         <f>IFERROR(VLOOKUP(A10,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S10" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="124">
-        <f>P10-Q10-R10-S10</f>
+      <c r="T10" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="124">
+        <f>Q10-R10-S10-T10</f>
         <v/>
       </c>
     </row>
@@ -14454,53 +14488,57 @@
         <v/>
       </c>
       <c r="H11" s="5">
-        <f>IF(C11="月給",D11,IF(C11="日給",D11*E11,IF(C11="時給",IFERROR(VLOOKUP(A11,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A11,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C11="月給",D11,IF(C11="日給",D11*E11+IFERROR(VLOOKUP(A11,従業員マスタ!$A:$G,7,0),0)*G11*8,IF(C11="時給",IFERROR(VLOOKUP(A11,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A11,月次集計!$A:$T,20,0),0)+G11*5),0),0)))</f>
         <v/>
       </c>
       <c r="I11" s="5">
-        <f>IFERROR(VLOOKUP(A11,従業員マスタ!$A:$G,7,0)*F11*1.25,0)</f>
+        <f>IF(OR(A11="EMP001",A11="EMP002"),0,IF(C11="時給",0,IFERROR(VLOOKUP(A11,従業員マスタ!$A:$G,7,0)*F11*1.25,0)))</f>
         <v/>
       </c>
       <c r="J11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="5">
-        <f>H11+I11+J11</f>
+      <c r="K11" s="32">
+        <f>IF(OR(A11="EMP008",A11="EMP009",A11="EMP010",A11="EMP011",A11="EMP012",A11="EMP016"),IFERROR(VLOOKUP(A11,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A11,月次集計!$A:$G,7,0)*8+VLOOKUP(A11,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L11" s="5">
+        <f>H11+I11+J11-K11</f>
+        <v/>
+      </c>
+      <c r="M11" s="5">
         <f>IFERROR(VLOOKUP(A11,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M11" s="5">
+      <c r="N11" s="5">
         <f>IFERROR(VLOOKUP(A11,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N11" s="5">
-        <f>IFERROR(ROUND(K11*VLOOKUP(A11,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O11" s="5">
+        <f>IFERROR(ROUND(L11*VLOOKUP(A11,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P11" s="5">
         <f>IFERROR(VLOOKUP(A11,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P11" s="5">
-        <f>K11-L11-M11-N11-O11</f>
-        <v/>
-      </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="5">
+        <f>L11-M11-N11-O11-P11</f>
+        <v/>
+      </c>
+      <c r="R11" s="122">
         <f>IFERROR(VLOOKUP(A11,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R11" s="122">
+      <c r="S11" s="122">
         <f>IFERROR(VLOOKUP(A11,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S11" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="124">
-        <f>P11-Q11-R11-S11</f>
+      <c r="T11" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="124">
+        <f>Q11-R11-S11-T11</f>
         <v/>
       </c>
     </row>
@@ -14535,53 +14573,57 @@
         <v/>
       </c>
       <c r="H12" s="32">
-        <f>IF(C12="月給",D12,IF(C12="日給",D12*E12,IF(C12="時給",IFERROR(VLOOKUP(A12,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A12,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C12="月給",D12,IF(C12="日給",D12*E12+IFERROR(VLOOKUP(A12,従業員マスタ!$A:$G,7,0),0)*G12*8,IF(C12="時給",IFERROR(VLOOKUP(A12,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A12,月次集計!$A:$T,20,0),0)+G12*5),0),0)))</f>
         <v/>
       </c>
       <c r="I12" s="32">
-        <f>IFERROR(VLOOKUP(A12,従業員マスタ!$A:$G,7,0)*F12*1.25,0)</f>
+        <f>IF(OR(A12="EMP001",A12="EMP002"),0,IF(C12="時給",0,IFERROR(VLOOKUP(A12,従業員マスタ!$A:$G,7,0)*F12*1.25,0)))</f>
         <v/>
       </c>
       <c r="J12" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="32">
-        <f>H12+I12+J12</f>
+        <f>IF(OR(A12="EMP008",A12="EMP009",A12="EMP010",A12="EMP011",A12="EMP012",A12="EMP016"),IFERROR(VLOOKUP(A12,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A12,月次集計!$A:$G,7,0)*8+VLOOKUP(A12,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L12" s="32">
+        <f>H12+I12+J12-K12</f>
+        <v/>
+      </c>
+      <c r="M12" s="32">
         <f>IFERROR(VLOOKUP(A12,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M12" s="32">
+      <c r="N12" s="32">
         <f>IFERROR(VLOOKUP(A12,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N12" s="32">
-        <f>IFERROR(ROUND(K12*VLOOKUP(A12,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O12" s="32">
+        <f>IFERROR(ROUND(L12*VLOOKUP(A12,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P12" s="32">
         <f>IFERROR(VLOOKUP(A12,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P12" s="32">
-        <f>K12-L12-M12-N12-O12</f>
-        <v/>
-      </c>
-      <c r="Q12" s="122">
+      <c r="Q12" s="32">
+        <f>L12-M12-N12-O12-P12</f>
+        <v/>
+      </c>
+      <c r="R12" s="122">
         <f>IFERROR(VLOOKUP(A12,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R12" s="122">
+      <c r="S12" s="122">
         <f>IFERROR(VLOOKUP(A12,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S12" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="124">
-        <f>P12-Q12-R12-S12</f>
+      <c r="T12" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="124">
+        <f>Q12-R12-S12-T12</f>
         <v/>
       </c>
     </row>
@@ -14616,53 +14658,57 @@
         <v/>
       </c>
       <c r="H13" s="5">
-        <f>IF(C13="月給",D13,IF(C13="日給",D13*E13,IF(C13="時給",IFERROR(VLOOKUP(A13,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A13,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C13="月給",D13,IF(C13="日給",D13*E13+IFERROR(VLOOKUP(A13,従業員マスタ!$A:$G,7,0),0)*G13*8,IF(C13="時給",IFERROR(VLOOKUP(A13,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A13,月次集計!$A:$T,20,0),0)+G13*5),0),0)))</f>
         <v/>
       </c>
       <c r="I13" s="5">
-        <f>IFERROR(VLOOKUP(A13,従業員マスタ!$A:$G,7,0)*F13*1.25,0)</f>
+        <f>IF(OR(A13="EMP001",A13="EMP002"),0,IF(C13="時給",0,IFERROR(VLOOKUP(A13,従業員マスタ!$A:$G,7,0)*F13*1.25,0)))</f>
         <v/>
       </c>
       <c r="J13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="5">
-        <f>H13+I13+J13</f>
+      <c r="K13" s="32">
+        <f>IF(OR(A13="EMP008",A13="EMP009",A13="EMP010",A13="EMP011",A13="EMP012",A13="EMP016"),IFERROR(VLOOKUP(A13,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A13,月次集計!$A:$G,7,0)*8+VLOOKUP(A13,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L13" s="5">
+        <f>H13+I13+J13-K13</f>
+        <v/>
+      </c>
+      <c r="M13" s="5">
         <f>IFERROR(VLOOKUP(A13,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M13" s="5">
+      <c r="N13" s="5">
         <f>IFERROR(VLOOKUP(A13,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N13" s="5">
-        <f>IFERROR(ROUND(K13*VLOOKUP(A13,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O13" s="5">
+        <f>IFERROR(ROUND(L13*VLOOKUP(A13,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P13" s="5">
         <f>IFERROR(VLOOKUP(A13,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P13" s="5">
-        <f>K13-L13-M13-N13-O13</f>
-        <v/>
-      </c>
-      <c r="Q13" s="122">
+      <c r="Q13" s="5">
+        <f>L13-M13-N13-O13-P13</f>
+        <v/>
+      </c>
+      <c r="R13" s="122">
         <f>IFERROR(VLOOKUP(A13,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R13" s="122">
+      <c r="S13" s="122">
         <f>IFERROR(VLOOKUP(A13,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S13" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="124">
-        <f>P13-Q13-R13-S13</f>
+      <c r="T13" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="124">
+        <f>Q13-R13-S13-T13</f>
         <v/>
       </c>
     </row>
@@ -14697,53 +14743,57 @@
         <v/>
       </c>
       <c r="H14" s="32">
-        <f>IF(C14="月給",D14,IF(C14="日給",D14*E14,IF(C14="時給",IFERROR(VLOOKUP(A14,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A14,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C14="月給",D14,IF(C14="日給",D14*E14+IFERROR(VLOOKUP(A14,従業員マスタ!$A:$G,7,0),0)*G14*8,IF(C14="時給",IFERROR(VLOOKUP(A14,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A14,月次集計!$A:$T,20,0),0)+G14*5),0),0)))</f>
         <v/>
       </c>
       <c r="I14" s="32">
-        <f>IFERROR(VLOOKUP(A14,従業員マスタ!$A:$G,7,0)*F14*1.25,0)</f>
+        <f>IF(OR(A14="EMP001",A14="EMP002"),0,IF(C14="時給",0,IFERROR(VLOOKUP(A14,従業員マスタ!$A:$G,7,0)*F14*1.25,0)))</f>
         <v/>
       </c>
       <c r="J14" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="32">
-        <f>H14+I14+J14</f>
+        <f>IF(OR(A14="EMP008",A14="EMP009",A14="EMP010",A14="EMP011",A14="EMP012",A14="EMP016"),IFERROR(VLOOKUP(A14,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A14,月次集計!$A:$G,7,0)*8+VLOOKUP(A14,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L14" s="32">
+        <f>H14+I14+J14-K14</f>
+        <v/>
+      </c>
+      <c r="M14" s="32">
         <f>IFERROR(VLOOKUP(A14,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M14" s="32">
+      <c r="N14" s="32">
         <f>IFERROR(VLOOKUP(A14,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N14" s="32">
-        <f>IFERROR(ROUND(K14*VLOOKUP(A14,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O14" s="32">
+        <f>IFERROR(ROUND(L14*VLOOKUP(A14,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="32">
         <f>IFERROR(VLOOKUP(A14,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P14" s="32">
-        <f>K14-L14-M14-N14-O14</f>
-        <v/>
-      </c>
-      <c r="Q14" s="122">
+      <c r="Q14" s="32">
+        <f>L14-M14-N14-O14-P14</f>
+        <v/>
+      </c>
+      <c r="R14" s="122">
         <f>IFERROR(VLOOKUP(A14,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R14" s="122">
+      <c r="S14" s="122">
         <f>IFERROR(VLOOKUP(A14,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S14" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="124">
-        <f>P14-Q14-R14-S14</f>
+      <c r="T14" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="124">
+        <f>Q14-R14-S14-T14</f>
         <v/>
       </c>
     </row>
@@ -14778,53 +14828,57 @@
         <v/>
       </c>
       <c r="H15" s="5">
-        <f>IF(C15="月給",D15,IF(C15="日給",D15*E15,IF(C15="時給",IFERROR(VLOOKUP(A15,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A15,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C15="月給",D15,IF(C15="日給",D15*E15+IFERROR(VLOOKUP(A15,従業員マスタ!$A:$G,7,0),0)*G15*8,IF(C15="時給",IFERROR(VLOOKUP(A15,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A15,月次集計!$A:$T,20,0),0)+G15*5),0),0)))</f>
         <v/>
       </c>
       <c r="I15" s="5">
-        <f>IFERROR(VLOOKUP(A15,従業員マスタ!$A:$G,7,0)*F15*1.25,0)</f>
+        <f>IF(OR(A15="EMP001",A15="EMP002"),0,IF(C15="時給",0,IFERROR(VLOOKUP(A15,従業員マスタ!$A:$G,7,0)*F15*1.25,0)))</f>
         <v/>
       </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="5">
-        <f>H15+I15+J15</f>
+      <c r="K15" s="32">
+        <f>IF(OR(A15="EMP008",A15="EMP009",A15="EMP010",A15="EMP011",A15="EMP012",A15="EMP016"),IFERROR(VLOOKUP(A15,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A15,月次集計!$A:$G,7,0)*8+VLOOKUP(A15,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L15" s="5">
+        <f>H15+I15+J15-K15</f>
+        <v/>
+      </c>
+      <c r="M15" s="5">
         <f>IFERROR(VLOOKUP(A15,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M15" s="5">
+      <c r="N15" s="5">
         <f>IFERROR(VLOOKUP(A15,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N15" s="5">
-        <f>IFERROR(ROUND(K15*VLOOKUP(A15,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O15" s="5">
+        <f>IFERROR(ROUND(L15*VLOOKUP(A15,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P15" s="5">
         <f>IFERROR(VLOOKUP(A15,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P15" s="5">
-        <f>K15-L15-M15-N15-O15</f>
-        <v/>
-      </c>
-      <c r="Q15" s="122">
+      <c r="Q15" s="5">
+        <f>L15-M15-N15-O15-P15</f>
+        <v/>
+      </c>
+      <c r="R15" s="122">
         <f>IFERROR(VLOOKUP(A15,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R15" s="122">
+      <c r="S15" s="122">
         <f>IFERROR(VLOOKUP(A15,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S15" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="124">
-        <f>P15-Q15-R15-S15</f>
+      <c r="T15" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="124">
+        <f>Q15-R15-S15-T15</f>
         <v/>
       </c>
     </row>
@@ -14859,53 +14913,57 @@
         <v/>
       </c>
       <c r="H16" s="32">
-        <f>IF(C16="月給",D16,IF(C16="日給",D16*E16,IF(C16="時給",IFERROR(VLOOKUP(A16,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A16,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C16="月給",D16,IF(C16="日給",D16*E16+IFERROR(VLOOKUP(A16,従業員マスタ!$A:$G,7,0),0)*G16*8,IF(C16="時給",IFERROR(VLOOKUP(A16,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A16,月次集計!$A:$T,20,0),0)+G16*5),0),0)))</f>
         <v/>
       </c>
       <c r="I16" s="32">
-        <f>IFERROR(VLOOKUP(A16,従業員マスタ!$A:$G,7,0)*F16*1.25,0)</f>
+        <f>IF(OR(A16="EMP001",A16="EMP002"),0,IF(C16="時給",0,IFERROR(VLOOKUP(A16,従業員マスタ!$A:$G,7,0)*F16*1.25,0)))</f>
         <v/>
       </c>
       <c r="J16" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="32">
-        <f>H16+I16+J16</f>
+        <f>IF(OR(A16="EMP008",A16="EMP009",A16="EMP010",A16="EMP011",A16="EMP012",A16="EMP016"),IFERROR(VLOOKUP(A16,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A16,月次集計!$A:$G,7,0)*8+VLOOKUP(A16,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L16" s="32">
+        <f>H16+I16+J16-K16</f>
+        <v/>
+      </c>
+      <c r="M16" s="32">
         <f>IFERROR(VLOOKUP(A16,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M16" s="32">
+      <c r="N16" s="32">
         <f>IFERROR(VLOOKUP(A16,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N16" s="32">
-        <f>IFERROR(ROUND(K16*VLOOKUP(A16,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O16" s="32">
+        <f>IFERROR(ROUND(L16*VLOOKUP(A16,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P16" s="32">
         <f>IFERROR(VLOOKUP(A16,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P16" s="32">
-        <f>K16-L16-M16-N16-O16</f>
-        <v/>
-      </c>
-      <c r="Q16" s="122">
+      <c r="Q16" s="32">
+        <f>L16-M16-N16-O16-P16</f>
+        <v/>
+      </c>
+      <c r="R16" s="122">
         <f>IFERROR(VLOOKUP(A16,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R16" s="122">
+      <c r="S16" s="122">
         <f>IFERROR(VLOOKUP(A16,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S16" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="124">
-        <f>P16-Q16-R16-S16</f>
+      <c r="T16" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="124">
+        <f>Q16-R16-S16-T16</f>
         <v/>
       </c>
     </row>
@@ -14940,53 +14998,57 @@
         <v/>
       </c>
       <c r="H17" s="5">
-        <f>IF(C17="月給",D17,IF(C17="日給",D17*E17,IF(C17="時給",IFERROR(VLOOKUP(A17,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A17,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C17="月給",D17,IF(C17="日給",D17*E17+IFERROR(VLOOKUP(A17,従業員マスタ!$A:$G,7,0),0)*G17*8,IF(C17="時給",IFERROR(VLOOKUP(A17,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A17,月次集計!$A:$T,20,0),0)+G17*5),0),0)))</f>
         <v/>
       </c>
       <c r="I17" s="5">
-        <f>IFERROR(VLOOKUP(A17,従業員マスタ!$A:$G,7,0)*F17*1.25,0)</f>
+        <f>IF(OR(A17="EMP001",A17="EMP002"),0,IF(C17="時給",0,IFERROR(VLOOKUP(A17,従業員マスタ!$A:$G,7,0)*F17*1.25,0)))</f>
         <v/>
       </c>
       <c r="J17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="5">
-        <f>H17+I17+J17</f>
+      <c r="K17" s="32">
+        <f>IF(OR(A17="EMP008",A17="EMP009",A17="EMP010",A17="EMP011",A17="EMP012",A17="EMP016"),IFERROR(VLOOKUP(A17,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A17,月次集計!$A:$G,7,0)*8+VLOOKUP(A17,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L17" s="5">
+        <f>H17+I17+J17-K17</f>
+        <v/>
+      </c>
+      <c r="M17" s="5">
         <f>IFERROR(VLOOKUP(A17,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M17" s="5">
+      <c r="N17" s="5">
         <f>IFERROR(VLOOKUP(A17,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N17" s="5">
-        <f>IFERROR(ROUND(K17*VLOOKUP(A17,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O17" s="5">
+        <f>IFERROR(ROUND(L17*VLOOKUP(A17,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P17" s="5">
         <f>IFERROR(VLOOKUP(A17,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P17" s="5">
-        <f>K17-L17-M17-N17-O17</f>
-        <v/>
-      </c>
-      <c r="Q17" s="122">
+      <c r="Q17" s="5">
+        <f>L17-M17-N17-O17-P17</f>
+        <v/>
+      </c>
+      <c r="R17" s="122">
         <f>IFERROR(VLOOKUP(A17,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R17" s="122">
+      <c r="S17" s="122">
         <f>IFERROR(VLOOKUP(A17,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S17" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="124">
-        <f>P17-Q17-R17-S17</f>
+      <c r="T17" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="124">
+        <f>Q17-R17-S17-T17</f>
         <v/>
       </c>
     </row>
@@ -15021,53 +15083,57 @@
         <v/>
       </c>
       <c r="H18" s="32">
-        <f>IF(C18="月給",D18,IF(C18="日給",D18*E18,IF(C18="時給",IFERROR(VLOOKUP(A18,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A18,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C18="月給",D18,IF(C18="日給",D18*E18+IFERROR(VLOOKUP(A18,従業員マスタ!$A:$G,7,0),0)*G18*8,IF(C18="時給",IFERROR(VLOOKUP(A18,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A18,月次集計!$A:$T,20,0),0)+G18*5),0),0)))</f>
         <v/>
       </c>
       <c r="I18" s="32">
-        <f>IFERROR(VLOOKUP(A18,従業員マスタ!$A:$G,7,0)*F18*1.25,0)</f>
+        <f>IF(OR(A18="EMP001",A18="EMP002"),0,IF(C18="時給",0,IFERROR(VLOOKUP(A18,従業員マスタ!$A:$G,7,0)*F18*1.25,0)))</f>
         <v/>
       </c>
       <c r="J18" s="32" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="32">
-        <f>H18+I18+J18</f>
+        <f>IF(OR(A18="EMP008",A18="EMP009",A18="EMP010",A18="EMP011",A18="EMP012",A18="EMP016"),IFERROR(VLOOKUP(A18,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A18,月次集計!$A:$G,7,0)*8+VLOOKUP(A18,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L18" s="32">
+        <f>H18+I18+J18-K18</f>
+        <v/>
+      </c>
+      <c r="M18" s="32">
         <f>IFERROR(VLOOKUP(A18,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M18" s="32">
+      <c r="N18" s="32">
         <f>IFERROR(VLOOKUP(A18,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N18" s="32">
-        <f>IFERROR(ROUND(K18*VLOOKUP(A18,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O18" s="32">
+        <f>IFERROR(ROUND(L18*VLOOKUP(A18,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P18" s="32">
         <f>IFERROR(VLOOKUP(A18,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P18" s="32">
-        <f>K18-L18-M18-N18-O18</f>
-        <v/>
-      </c>
-      <c r="Q18" s="122">
+      <c r="Q18" s="32">
+        <f>L18-M18-N18-O18-P18</f>
+        <v/>
+      </c>
+      <c r="R18" s="122">
         <f>IFERROR(VLOOKUP(A18,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R18" s="122">
+      <c r="S18" s="122">
         <f>IFERROR(VLOOKUP(A18,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S18" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="124">
-        <f>P18-Q18-R18-S18</f>
+      <c r="T18" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="124">
+        <f>Q18-R18-S18-T18</f>
         <v/>
       </c>
     </row>
@@ -15102,53 +15168,57 @@
         <v/>
       </c>
       <c r="H19" s="5">
-        <f>IF(C19="月給",D19,IF(C19="日給",D19*E19,IF(C19="時給",IFERROR(VLOOKUP(A19,従業員マスタ!$A:$G,7,0)*IFERROR(VLOOKUP(A19,月次集計!$A:$T,20,0),0),0),0)))</f>
+        <f>IF(C19="月給",D19,IF(C19="日給",D19*E19+IFERROR(VLOOKUP(A19,従業員マスタ!$A:$G,7,0),0)*G19*8,IF(C19="時給",IFERROR(VLOOKUP(A19,従業員マスタ!$A:$G,7,0)*(IFERROR(VLOOKUP(A19,月次集計!$A:$T,20,0),0)+G19*5),0),0)))</f>
         <v/>
       </c>
       <c r="I19" s="5">
-        <f>IFERROR(VLOOKUP(A19,従業員マスタ!$A:$G,7,0)*F19*1.25,0)</f>
+        <f>IF(OR(A19="EMP001",A19="EMP002"),0,IF(C19="時給",0,IFERROR(VLOOKUP(A19,従業員マスタ!$A:$G,7,0)*F19*1.25,0)))</f>
         <v/>
       </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="5">
-        <f>H19+I19+J19</f>
+      <c r="K19" s="32">
+        <f>IF(OR(A19="EMP008",A19="EMP009",A19="EMP010",A19="EMP011",A19="EMP012",A19="EMP016"),IFERROR(VLOOKUP(A19,従業員マスタ!$A:$G,7,0)*(VLOOKUP(A19,月次集計!$A:$G,7,0)*8+VLOOKUP(A19,月次集計!$A:$I,9,0)),0),0)</f>
         <v/>
       </c>
       <c r="L19" s="5">
+        <f>H19+I19+J19-K19</f>
+        <v/>
+      </c>
+      <c r="M19" s="5">
         <f>IFERROR(VLOOKUP(A19,従業員マスタ!$A:$I,8,0),0)</f>
         <v/>
       </c>
-      <c r="M19" s="5">
+      <c r="N19" s="5">
         <f>IFERROR(VLOOKUP(A19,従業員マスタ!$A:$J,9,0),0)</f>
         <v/>
       </c>
-      <c r="N19" s="5">
-        <f>IFERROR(ROUND(K19*VLOOKUP(A19,従業員マスタ!$A:$K,10,0),0),0)</f>
-        <v/>
-      </c>
       <c r="O19" s="5">
+        <f>IFERROR(ROUND(L19*VLOOKUP(A19,従業員マスタ!$A:$K,10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="P19" s="5">
         <f>IFERROR(VLOOKUP(A19,従業員マスタ!$A:$L,11,0),0)</f>
         <v/>
       </c>
-      <c r="P19" s="5">
-        <f>K19-L19-M19-N19-O19</f>
-        <v/>
-      </c>
-      <c r="Q19" s="122">
+      <c r="Q19" s="5">
+        <f>L19-M19-N19-O19-P19</f>
+        <v/>
+      </c>
+      <c r="R19" s="122">
         <f>IFERROR(VLOOKUP(A19,従業員マスタ!$A:$L,12,0),0)</f>
         <v/>
       </c>
-      <c r="R19" s="122">
+      <c r="S19" s="122">
         <f>IFERROR(VLOOKUP(A19,従業員マスタ!$A:$M,13,0),0)</f>
         <v/>
       </c>
-      <c r="S19" s="123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="124">
-        <f>P19-Q19-R19-S19</f>
+      <c r="T19" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="124">
+        <f>Q19-R19-S19-T19</f>
         <v/>
       </c>
     </row>
@@ -15188,7 +15258,7 @@
         <f>SUM(J4:J19)</f>
         <v/>
       </c>
-      <c r="K20" s="34">
+      <c r="K20" s="32">
         <f>SUM(K4:K19)</f>
         <v/>
       </c>
@@ -15212,7 +15282,7 @@
         <f>SUM(P4:P19)</f>
         <v/>
       </c>
-      <c r="Q20" s="126">
+      <c r="Q20" s="34">
         <f>SUM(Q4:Q19)</f>
         <v/>
       </c>
@@ -15226,6 +15296,10 @@
       </c>
       <c r="T20" s="126">
         <f>SUM(T4:T19)</f>
+        <v/>
+      </c>
+      <c r="U20" s="126">
+        <f>SUM(U4:U19)</f>
         <v/>
       </c>
     </row>

--- a/給与管理システム_v3.xlsx
+++ b/給与管理システム_v3.xlsx
@@ -3394,22 +3394,22 @@
     <row r="7" ht="21.75" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>EMP005</t>
+          <t>EMP007</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>廣瀬 伸二</t>
+          <t>中原 宏</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>ヒロセ シンジ</t>
+          <t>ナカハラ ヒロシ</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>月給</t>
+          <t>日給</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -3417,38 +3417,60 @@
           <t>在籍</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
+      <c r="F7" s="5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>12132</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>21960</t>
+        </is>
+      </c>
       <c r="J7" s="108" t="n">
         <v>0.006</v>
       </c>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="2" t="n"/>
+      <c r="K7" s="5" t="n">
+        <v>4050</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2019/04/01</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="n"/>
     </row>
     <row r="8" ht="21.75" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>EMP006</t>
+          <t>EMP008</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>山田 一光</t>
+          <t>アルフィアン ソレフル ハディ</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>ヤマダ カズミツ</t>
+          <t>アルフィアン</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>日給</t>
+          <t>月給</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -3457,59 +3479,57 @@
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>11000</v>
+        <v>216667</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>1375</v>
+        <v>1250</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="J8" s="109" t="n">
         <v>0.006</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>0</v>
+        <v>3550</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>3800</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>2018/04/01</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="n"/>
+        <v>1200</v>
+      </c>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>実習生</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="21.75" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EMP007</t>
+          <t>EMP009</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>中原 宏</t>
+          <t>ムハンマド ヨザテュル イスラム</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ナカハラ ヒロシ</t>
+          <t>ヨザ</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>日給</t>
+          <t>月給</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -3518,54 +3538,52 @@
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>12000</v>
+        <v>216667</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1500</v>
+        <v>1250</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="J9" s="108" t="n">
         <v>0.006</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>4050</v>
+        <v>1940</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2019/04/01</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="n"/>
+        <v>1200</v>
+      </c>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>実習生</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="21.75" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>EMP008</t>
+          <t>EMP010</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>アルフィアン ソレフル ハディ</t>
+          <t>リズキ ノビアント</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>アルフィアン</t>
+          <t>リズキ</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -3579,29 +3597,29 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>216667</v>
+        <v>183214</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>1250</v>
+        <v>1057</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="J10" s="109" t="n">
         <v>0.006</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>3550</v>
+        <v>910</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="7" t="n"/>
@@ -3614,17 +3632,17 @@
     <row r="11" ht="21.75" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EMP009</t>
+          <t>EMP011</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ムハンマド ヨザテュル イスラム</t>
+          <t>ディマス サトリオ ブアナ</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ヨザ</t>
+          <t>ディマス</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3638,29 +3656,29 @@
         </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>216667</v>
+        <v>183214</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1250</v>
+        <v>1057</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="J11" s="108" t="n">
         <v>0.006</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1940</v>
+        <v>810</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="2" t="n"/>
@@ -3673,22 +3691,22 @@
     <row r="12" ht="21.75" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>EMP010</t>
+          <t>EMP012</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>リズキ ノビアント</t>
+          <t>山田 ユカリ</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>リズキ</t>
+          <t>ヤマダ ユカリ</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>月給</t>
+          <t>時給</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -3696,58 +3714,40 @@
           <t>在籍</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>183214</v>
-      </c>
+      <c r="F12" s="10" t="n"/>
       <c r="G12" s="10" t="n">
-        <v>1057</v>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>8593</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>15555</t>
-        </is>
-      </c>
+        <v>1429</v>
+      </c>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
       <c r="J12" s="109" t="n">
         <v>0.006</v>
       </c>
-      <c r="K12" s="10" t="n">
-        <v>910</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="7" t="n"/>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>実習生</t>
-        </is>
-      </c>
+      <c r="O12" s="8" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EMP011</t>
+          <t>EMP013</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ディマス サトリオ ブアナ</t>
+          <t>菊川 裕美</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ディマス</t>
+          <t>キクカワ ユミ</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>月給</t>
+          <t>時給</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -3755,58 +3755,40 @@
           <t>在籍</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n">
-        <v>183214</v>
-      </c>
+      <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n">
-        <v>1057</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>8593</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>15555</t>
-        </is>
-      </c>
+        <v>1100</v>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
       <c r="J13" s="108" t="n">
         <v>0.006</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v>810</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="2" t="n"/>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>実習生</t>
-        </is>
-      </c>
+      <c r="O13" s="3" t="n"/>
     </row>
     <row r="14" ht="21.75" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>EMP012</t>
+          <t>EMP014</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>山田 ユカリ</t>
+          <t>中島 孝信</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>ヤマダ ユカリ</t>
+          <t>ナカシマ タカノブ</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>時給</t>
+          <t>月給</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -3814,40 +3796,56 @@
           <t>在籍</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n">
-        <v>1429</v>
-      </c>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
+      <c r="F14" s="10" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J14" s="109" t="n">
         <v>0.006</v>
       </c>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="10" t="n"/>
+      <c r="K14" s="10" t="n">
+        <v>7820</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="M14" s="10" t="n"/>
       <c r="N14" s="7" t="n"/>
-      <c r="O14" s="8" t="n"/>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>年1回一括支払</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="21.75" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EMP013</t>
+          <t>EMP015</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>菊川 裕美</t>
+          <t>中原 廣子</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>キクカワ ユミ</t>
+          <t>ナカハラ ヒロコ</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>時給</t>
+          <t>月給</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -3855,17 +3853,29 @@
           <t>在籍</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
+      <c r="F15" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J15" s="108" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="3" t="n"/>
@@ -3873,17 +3883,17 @@
     <row r="16" ht="21.75" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>EMP014</t>
+          <t>EMP016</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>中島 孝信</t>
+          <t>畑野 浩次</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>ナカシマ タカノブ</t>
+          <t>ハタノ コウジ</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -3897,55 +3907,39 @@
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="10" t="n"/>
       <c r="J16" s="109" t="n">
         <v>0.006</v>
       </c>
-      <c r="K16" s="10" t="n">
-        <v>7820</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n"/>
       <c r="M16" s="10" t="n"/>
       <c r="N16" s="7" t="n"/>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>年1回一括支払</t>
-        </is>
-      </c>
+      <c r="O16" s="8" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EMP015</t>
+          <t>EMP017</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>中原 廣子</t>
+          <t>濱津 紀子</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>ナカハラ ヒロコ</t>
+          <t>ハマツ ノリコ</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>月給</t>
+          <t>時給</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -3953,114 +3947,20 @@
           <t>在籍</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>60000</v>
-      </c>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n">
+        <v>1057</v>
+      </c>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
       <c r="J17" s="108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>0.006</v>
+      </c>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="21.75" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>EMP016</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>畑野 浩次</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>ハタノ コウジ</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>月給</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>在籍</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="109" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n"/>
-      <c r="M18" s="10" t="n"/>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="21.75" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>EMP017</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>濱津 紀子</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>ハマツ ノリコ</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>時給</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>在籍</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n">
-        <v>1057</v>
-      </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="108" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
